--- a/artfynd/A 8764-2026 artfynd.xlsx
+++ b/artfynd/A 8764-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17145600</v>
+        <v>93551711</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>381</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stor vårtrattskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Rhizocybe vermicularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Vizzini &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rättviksheden, kalkverket S, Dlr</t>
+          <t>Rättvik, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508942.0656374237</v>
+        <v>508944</v>
       </c>
       <c r="R2" t="n">
-        <v>6751991.697658136</v>
+        <v>6752001</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-09-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Släta - rutiga fruktkroppar.</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,24 +766,466 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Tallhed</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Paula Ryökäs</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Paula Ryökäs</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>61803790</v>
+      </c>
+      <c r="B3" t="n">
+        <v>87238</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>445</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kopparspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius cupreorufus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rättviksheden, Kalkverket S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>508954</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6751957</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>SMF kurs Svampar i sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Örjan Fritz, Elisabet Ottosson, Johan Nitare, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>103478415</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93196</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1435</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bitter taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum fennicum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rättvik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>508972</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6751971</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stina Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stina Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>17145600</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rättviksheden, kalkverket S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>508942</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6751992</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2011-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2011-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Släta - rutiga fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tallhed</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Anita Stridvall</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Anita Stridvall, Stig Jacobsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>61803791</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93193</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rättviksheden, Kalkverket S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>508954</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6751957</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>SMF kurs Svampar i sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Örjan Fritz, Elisabet Ottosson, Johan Nitare, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8764-2026 artfynd.xlsx
+++ b/artfynd/A 8764-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93551711</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61803790</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103478415</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17145600</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,8 +1251,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61803791</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>